--- a/Resources/Budget_Template.xlsx
+++ b/Resources/Budget_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63d545a1e0281ec1/Documents/GitHub/Onyx-Projects/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="8_{05FA1DFA-E93A-4EBB-9964-83706091560C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCFF53E6-4367-43C0-830C-2128659DA35D}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="8_{05FA1DFA-E93A-4EBB-9964-83706091560C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD90176B-6A0A-4B0B-B073-9E9A74CAF64F}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="15585" activeTab="1" xr2:uid="{9D8D3B20-2C41-4894-A29D-76A3FE1B9FBA}"/>
+    <workbookView xWindow="-51735" yWindow="-1710" windowWidth="51870" windowHeight="21150" activeTab="1" xr2:uid="{9D8D3B20-2C41-4894-A29D-76A3FE1B9FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="January 2026" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="101">
   <si>
     <t>Accounting Report</t>
   </si>
@@ -336,120 +336,6 @@
   </si>
   <si>
     <t>Gas Utility</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal SNAPPY / STORE 9715 KAW DR EDWARDSVILLE KSUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal SANTA / FE TOW SERVIC913-8945201 KSUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / O'REILLY 1893 OVERLAND PARK KSUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal GOOGLE / *ADS31474 Mountain View CAUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / HIS*HISCOX INC 888-202-3007 NYUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Deposit WORKIZ / iNC San Diego CAUS</t>
-  </si>
-  <si>
-    <t>Withdrawal Internet Transfer TO / : XXXX3271</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal VENMO / *Alex LocksmiNew York NYUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal VENMO / *Armani MartiVisa Direct NYUS</t>
-  </si>
-  <si>
-    <t>Check #104: Check</t>
-  </si>
-  <si>
-    <t>Deposit ITM ID 00446-KS000211i / ITM Session 19466998</t>
-  </si>
-  <si>
-    <t>Withdrawal Internet Transfer TO / : XXXX1758</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal QT 182 / OUTSIDE OLATHE KSUS</t>
-  </si>
-  <si>
-    <t>ACH Deposit Workiz Inc. - / TRANSFER ST-X5C8N1F2E5S9</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / VISTAPRINT 866-207-4955 MAUS</t>
-  </si>
-  <si>
-    <t>ACH Payment EVERGY KS CTRL / EVERGY KS CTRL AUTOP - AUTOPAY</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal IMLSS / UTAH 801-486-0079 UTUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / AMAZON.COM SEATTLE WAUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / SHAWNEE MISSION FOR501-3379600 KSUS</t>
-  </si>
-  <si>
-    <t>ACH Payment ATMOS ENERGY SGL - / UTIL PYMT</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / UHSHARD* 954-866-2300 ILUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal KANSAS / SEC OF STATE785-296-6187 KSUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / APPLE.COM/BILL 866-712-7753 CAUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / WEB*BLUEHOST.COM 888-4014678 UTUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal FACEBK / *ESWV5FRZ Wilmington DEUS</t>
-  </si>
-  <si>
-    <t>International Fee NonUS Funds / International Fee Non US Funds</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / QRA*HKDMOSSGYRE HONG KONG HKHK</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / VZWRLSS*APOCC VISB 800-922-0204 FLUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal WORKIZ / INC. WORKIZ.COM CAUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal FACEBK / *7ZZJHF5Z Wilmington DEUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / CLAUDE.AI SUBSCRIPTANTHROPIC.COM CAUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / MENARDS 3343 OLATHE KSUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal FACEBK / *4UXGSFVYJ2 6505434800 CAUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal FACEBK / *XDW7SFVY Wilmington DEUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal SNAPPY / STORE EDWARDSVILLE KSUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal FACEBK / *92HEGFRZ Wilmington DEUS</t>
-  </si>
-  <si>
-    <t>Point Of Sale Withdrawal / HEARTLAND PAWN &amp; JEOLATHE KSUS</t>
-  </si>
-  <si>
-    <t>Card Hold / NASTFSECURITYRE NASTFSECURITYREGIST+18102894809 COUS</t>
   </si>
   <si>
     <t>Fleet Maintenance</t>
@@ -1156,7 +1042,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1263,9 +1149,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1292,6 +1193,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1320,28 +1224,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1350,11 +1232,59 @@
   <dxfs count="20">
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1393,54 +1323,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2055,19 +1937,15 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C4698226-7A25-42AC-B1FB-F19B23D21CE6}" name="Table133" displayName="Table133" ref="J9:K37" totalsRowShown="0" headerRowDxfId="19" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C4698226-7A25-42AC-B1FB-F19B23D21CE6}" name="Table133" displayName="Table133" ref="J9:K37" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="J9:K37" xr:uid="{755695DB-3083-4866-B1AB-93CA5DBFF2AE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J10:K27">
     <sortCondition ref="K9:K27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{916BEFB9-7F12-48E8-BCF1-E8E99C6FFF5F}" name="Categories" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{C695EBFB-9E27-4FCC-970F-A1DA7F31E2DB}" name="Total Amount" dataDxfId="16" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{916BEFB9-7F12-48E8-BCF1-E8E99C6FFF5F}" name="Categories" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{C695EBFB-9E27-4FCC-970F-A1DA7F31E2DB}" name="Total Amount" dataDxfId="12" dataCellStyle="Currency">
       <calculatedColumnFormula>SUMIF($D$10:$D$116,J10,$F$10:$F$116)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2076,14 +1954,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09F825F1-0DFE-44B9-ABFF-6F0EF085391B}" name="Table1332" displayName="Table1332" ref="J9:K37" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09F825F1-0DFE-44B9-ABFF-6F0EF085391B}" name="Table1332" displayName="Table1332" ref="J9:K37" totalsRowShown="0" headerRowDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="J9:K37" xr:uid="{755695DB-3083-4866-B1AB-93CA5DBFF2AE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J10:K27">
     <sortCondition ref="K9:K27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B333F167-4289-4D02-98F0-C833764435B4}" name="Categories" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{A5D65F90-0C41-47B0-BC6A-7E2ECA4E2D73}" name="Total Amount" dataDxfId="12" dataCellStyle="Currency">
+    <tableColumn id="1" xr3:uid="{B333F167-4289-4D02-98F0-C833764435B4}" name="Categories" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{A5D65F90-0C41-47B0-BC6A-7E2ECA4E2D73}" name="Total Amount" dataDxfId="16" dataCellStyle="Currency">
       <calculatedColumnFormula>SUMIF($D$10:$D$116,J10,$F$10:$F$116)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2409,29 +2287,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005CB6D5-41C6-4E1A-BA4F-A230D5ABCD80}">
   <dimension ref="A1:AI139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
-    <col min="11" max="11" width="38.42578125" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" customWidth="1"/>
-    <col min="14" max="14" width="22.7109375" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" customWidth="1"/>
-    <col min="16" max="16" width="2.5703125" customWidth="1"/>
-    <col min="20" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="11" max="11" width="38.44140625" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" customWidth="1"/>
+    <col min="13" max="13" width="15.88671875" customWidth="1"/>
+    <col min="14" max="14" width="22.6640625" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" customWidth="1"/>
+    <col min="16" max="16" width="2.5546875" customWidth="1"/>
+    <col min="20" max="21" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="58"/>
-      <c r="B1" s="58"/>
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A1" s="79"/>
+      <c r="B1" s="79"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2465,22 +2343,22 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="68" t="s">
+    <row r="2" spans="1:35" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="70" t="s">
-        <v>138</v>
-      </c>
-      <c r="K2" s="70"/>
+      <c r="J2" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="82"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -2506,18 +2384,18 @@
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -2543,18 +2421,18 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -2580,18 +2458,18 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -2617,18 +2495,18 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
     </row>
-    <row r="6" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+    <row r="6" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -2654,7 +2532,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="55"/>
@@ -2691,7 +2569,7 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2726,7 +2604,7 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="31" t="s">
@@ -2779,7 +2657,7 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="34">
@@ -2795,12 +2673,12 @@
         <v>6859.88</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="80"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="82" t="s">
+      <c r="J10" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="89">
+      <c r="K10" s="68">
         <f>SUMIF($D$10:$D$117,J10,$F$10:$F$117)</f>
         <v>8411.7099999999991</v>
       </c>
@@ -2829,7 +2707,7 @@
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="36">
@@ -2847,18 +2725,18 @@
       <c r="G11" s="2"/>
       <c r="H11" s="35"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="82" t="s">
+      <c r="J11" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="88">
+      <c r="K11" s="67">
         <f>SUMIF($D$10:$D$117,J11,$F$10:$F$117)</f>
         <v>2600</v>
       </c>
       <c r="L11" s="41"/>
-      <c r="M11" s="72" t="s">
+      <c r="M11" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="72"/>
+      <c r="N11" s="84"/>
       <c r="O11" s="42"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -2881,7 +2759,7 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
     </row>
-    <row r="12" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="37">
@@ -2899,16 +2777,16 @@
       <c r="G12" s="2"/>
       <c r="H12" s="35"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="83" t="s">
+      <c r="J12" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="66">
         <f t="shared" ref="K12:K36" si="0">SUMIF($D$10:$D$117,J12,$F$10:$F$117)</f>
         <v>0</v>
       </c>
       <c r="L12" s="1"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="73"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
       <c r="O12" s="25"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -2931,7 +2809,7 @@
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="37">
@@ -2949,10 +2827,10 @@
       <c r="G13" s="2"/>
       <c r="H13" s="35"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="83" t="s">
+      <c r="J13" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="87">
+      <c r="K13" s="66">
         <f t="shared" si="0"/>
         <v>56.86</v>
       </c>
@@ -2986,7 +2864,7 @@
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
     </row>
-    <row r="14" spans="1:35" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="37">
@@ -3004,10 +2882,10 @@
       <c r="G14" s="2"/>
       <c r="H14" s="35"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="83" t="s">
+      <c r="J14" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="87">
+      <c r="K14" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3041,7 +2919,7 @@
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
     </row>
-    <row r="15" spans="1:35" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" ht="19.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="37">
@@ -3059,10 +2937,10 @@
       <c r="G15" s="2"/>
       <c r="H15" s="35"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="83" t="s">
+      <c r="J15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="87">
+      <c r="K15" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3096,7 +2974,7 @@
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="37">
@@ -3114,10 +2992,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="35"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="83" t="s">
+      <c r="J16" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="87">
+      <c r="K16" s="66">
         <f t="shared" si="0"/>
         <v>178.04</v>
       </c>
@@ -3146,7 +3024,7 @@
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="1:35" ht="20.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" ht="20.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="37">
@@ -3164,18 +3042,18 @@
       <c r="G17" s="2"/>
       <c r="H17" s="35"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="83" t="s">
+      <c r="J17" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="87">
+      <c r="K17" s="66">
         <f t="shared" si="0"/>
         <v>469.16</v>
       </c>
-      <c r="L17" s="85"/>
-      <c r="M17" s="74" t="s">
+      <c r="L17" s="64"/>
+      <c r="M17" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="N17" s="74"/>
+      <c r="N17" s="86"/>
       <c r="O17" s="27"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -3198,7 +3076,7 @@
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
     </row>
-    <row r="18" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="37">
@@ -3216,16 +3094,16 @@
       <c r="G18" s="2"/>
       <c r="H18" s="35"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="83" t="s">
+      <c r="J18" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="87">
+      <c r="K18" s="66">
         <f t="shared" si="0"/>
         <v>3285</v>
       </c>
-      <c r="L18" s="86"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="75"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
       <c r="O18" s="28"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -3248,7 +3126,7 @@
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
     </row>
-    <row r="19" spans="1:35" ht="20.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" ht="20.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="37">
@@ -3266,18 +3144,18 @@
       <c r="G19" s="2"/>
       <c r="H19" s="35"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="83" t="s">
+      <c r="J19" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L19" s="1"/>
-      <c r="M19" s="67" t="s">
+      <c r="M19" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="N19" s="76" t="s">
+      <c r="N19" s="88" t="s">
         <v>16</v>
       </c>
       <c r="O19" s="25"/>
@@ -3302,7 +3180,7 @@
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
     </row>
-    <row r="20" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="37">
@@ -3320,16 +3198,16 @@
       <c r="G20" s="2"/>
       <c r="H20" s="35"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="83" t="s">
+      <c r="J20" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="87">
+      <c r="K20" s="66">
         <f t="shared" si="0"/>
         <v>1611.31</v>
       </c>
       <c r="L20" s="1"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="76"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="88"/>
       <c r="O20" s="25"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -3352,7 +3230,7 @@
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
     </row>
-    <row r="21" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="37">
@@ -3370,19 +3248,19 @@
       <c r="G21" s="2"/>
       <c r="H21" s="35"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="83" t="s">
+      <c r="J21" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="87">
+      <c r="K21" s="66">
         <f t="shared" si="0"/>
         <v>75.210000000000008</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="65">
+      <c r="M21" s="76">
         <f>COUNTIF($D$11:$D$122, "Subscriptions")</f>
         <v>0</v>
       </c>
-      <c r="N21" s="66">
+      <c r="N21" s="77">
         <f>COUNTIF($D$11:$D$122, "Restaurant")</f>
         <v>0</v>
       </c>
@@ -3408,7 +3286,7 @@
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
     </row>
-    <row r="22" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="37">
@@ -3426,16 +3304,16 @@
       <c r="G22" s="2"/>
       <c r="H22" s="35"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="83" t="s">
+      <c r="J22" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="K22" s="87">
+      <c r="K22" s="66">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
       <c r="L22" s="1"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="66"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="77"/>
       <c r="O22" s="25"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -3458,7 +3336,7 @@
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
     </row>
-    <row r="23" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="37">
@@ -3476,10 +3354,10 @@
       <c r="G23" s="2"/>
       <c r="H23" s="35"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="83" t="s">
+      <c r="J23" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="K23" s="87">
+      <c r="K23" s="66">
         <f t="shared" si="0"/>
         <v>262.05</v>
       </c>
@@ -3508,7 +3386,7 @@
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
     </row>
-    <row r="24" spans="1:35" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="37">
@@ -3526,18 +3404,18 @@
       <c r="G24" s="2"/>
       <c r="H24" s="35"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="84" t="s">
+      <c r="J24" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="K24" s="87">
+      <c r="K24" s="66">
         <f t="shared" si="0"/>
         <v>8659.44</v>
       </c>
       <c r="L24" s="20"/>
-      <c r="M24" s="67" t="s">
+      <c r="M24" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="67" t="s">
+      <c r="N24" s="78" t="s">
         <v>20</v>
       </c>
       <c r="O24" s="25"/>
@@ -3562,7 +3440,7 @@
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
     </row>
-    <row r="25" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="37">
@@ -3580,16 +3458,16 @@
       <c r="G25" s="2"/>
       <c r="H25" s="35"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="84" t="s">
+      <c r="J25" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="87">
+      <c r="K25" s="66">
         <f t="shared" si="0"/>
         <v>388.25</v>
       </c>
       <c r="L25" s="20"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
+      <c r="M25" s="78"/>
+      <c r="N25" s="78"/>
       <c r="O25" s="25"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -3612,7 +3490,7 @@
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
     </row>
-    <row r="26" spans="1:35" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" ht="18.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="37">
@@ -3630,19 +3508,19 @@
       <c r="G26" s="2"/>
       <c r="H26" s="35"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="84" t="s">
+      <c r="J26" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="87">
+      <c r="K26" s="66">
         <f t="shared" si="0"/>
         <v>89.06</v>
       </c>
       <c r="L26" s="20"/>
-      <c r="M26" s="66">
+      <c r="M26" s="77">
         <f>COUNTIF($D$11:$D$122, "Gas")</f>
         <v>1</v>
       </c>
-      <c r="N26" s="66">
+      <c r="N26" s="77">
         <f>COUNTIF($D$11:$D$122, "Savings")</f>
         <v>0</v>
       </c>
@@ -3668,7 +3546,7 @@
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
     </row>
-    <row r="27" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="37">
@@ -3686,16 +3564,16 @@
       <c r="G27" s="2"/>
       <c r="H27" s="35"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="84" t="s">
+      <c r="J27" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="87">
+      <c r="K27" s="66">
         <f t="shared" si="0"/>
         <v>10.879999999999999</v>
       </c>
       <c r="L27" s="20"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
+      <c r="M27" s="77"/>
+      <c r="N27" s="77"/>
       <c r="O27" s="25"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -3718,7 +3596,7 @@
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
     </row>
-    <row r="28" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="37">
@@ -3736,16 +3614,16 @@
       <c r="G28" s="2"/>
       <c r="H28" s="35"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="83" t="s">
+      <c r="J28" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="K28" s="87">
+      <c r="K28" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L28" s="20"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
+      <c r="M28" s="77"/>
+      <c r="N28" s="77"/>
       <c r="O28" s="25"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -3768,7 +3646,7 @@
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
     </row>
-    <row r="29" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="37">
@@ -3786,16 +3664,16 @@
       <c r="G29" s="2"/>
       <c r="H29" s="35"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="87">
+      <c r="K29" s="66">
         <f t="shared" si="0"/>
         <v>144.12</v>
       </c>
-      <c r="L29" s="78"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
       <c r="O29" s="25"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -3818,7 +3696,7 @@
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
     </row>
-    <row r="30" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="37">
@@ -3836,16 +3714,16 @@
       <c r="G30" s="2"/>
       <c r="H30" s="35"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="83" t="s">
+      <c r="J30" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="K30" s="87">
+      <c r="K30" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L30" s="78"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="77"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
       <c r="O30" s="25"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -3868,7 +3746,7 @@
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
     </row>
-    <row r="31" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="37">
@@ -3886,16 +3764,16 @@
       <c r="G31" s="2"/>
       <c r="H31" s="35"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="83" t="s">
+      <c r="J31" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="87">
+      <c r="K31" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L31" s="78"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="77"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
       <c r="O31" s="25"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -3918,7 +3796,7 @@
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
     </row>
-    <row r="32" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="37">
@@ -3936,16 +3814,16 @@
       <c r="G32" s="2"/>
       <c r="H32" s="35"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="83" t="s">
+      <c r="J32" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="87">
+      <c r="K32" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L32" s="78"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
       <c r="O32" s="25"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -3968,7 +3846,7 @@
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
     </row>
-    <row r="33" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="37">
@@ -3986,16 +3864,16 @@
       <c r="G33" s="2"/>
       <c r="H33" s="35"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="83" t="s">
+      <c r="J33" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="K33" s="87">
+      <c r="K33" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L33" s="78"/>
-      <c r="M33" s="77"/>
-      <c r="N33" s="77"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="25"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -4018,7 +3896,7 @@
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
     </row>
-    <row r="34" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="37">
@@ -4036,16 +3914,16 @@
       <c r="G34" s="2"/>
       <c r="H34" s="35"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="K34" s="87">
+      <c r="K34" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L34" s="78"/>
-      <c r="M34" s="77"/>
-      <c r="N34" s="77"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
       <c r="O34" s="25"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -4068,7 +3946,7 @@
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
     </row>
-    <row r="35" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="37">
@@ -4086,16 +3964,16 @@
       <c r="G35" s="2"/>
       <c r="H35" s="35"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="83" t="s">
+      <c r="J35" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="87">
+      <c r="K35" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L35" s="78"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
       <c r="O35" s="25"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -4118,7 +3996,7 @@
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
     </row>
-    <row r="36" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="37">
@@ -4136,16 +4014,16 @@
       <c r="G36" s="2"/>
       <c r="H36" s="35"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="83" t="s">
+      <c r="J36" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="K36" s="87">
+      <c r="K36" s="66">
         <f t="shared" si="0"/>
         <v>1185.9100000000003</v>
       </c>
-      <c r="L36" s="78"/>
-      <c r="M36" s="77"/>
-      <c r="N36" s="77"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
       <c r="O36" s="25"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -4168,7 +4046,7 @@
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
     </row>
-    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="37">
@@ -4213,7 +4091,7 @@
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
     </row>
-    <row r="38" spans="1:35" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="37">
@@ -4231,12 +4109,12 @@
       <c r="G38" s="2"/>
       <c r="H38" s="35"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="62"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="73"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
@@ -4258,7 +4136,7 @@
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
     </row>
-    <row r="39" spans="1:35" ht="23.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="37">
@@ -4276,12 +4154,12 @@
       <c r="G39" s="2"/>
       <c r="H39" s="35"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="63"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="64"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="74"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="75"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
@@ -4303,7 +4181,7 @@
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
     </row>
-    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="37">
@@ -4348,7 +4226,7 @@
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
     </row>
-    <row r="41" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="37">
@@ -4393,7 +4271,7 @@
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
     </row>
-    <row r="42" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="37">
@@ -4438,7 +4316,7 @@
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
     </row>
-    <row r="43" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="37">
@@ -4483,7 +4361,7 @@
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
     </row>
-    <row r="44" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="37">
@@ -4528,7 +4406,7 @@
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
     </row>
-    <row r="45" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="37">
@@ -4575,7 +4453,7 @@
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
     </row>
-    <row r="46" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="37">
@@ -4620,7 +4498,7 @@
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
     </row>
-    <row r="47" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="37">
@@ -4665,7 +4543,7 @@
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
     </row>
-    <row r="48" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="37">
@@ -4710,7 +4588,7 @@
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
     </row>
-    <row r="49" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="37">
@@ -4755,7 +4633,7 @@
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
     </row>
-    <row r="50" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="37">
@@ -4800,7 +4678,7 @@
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
     </row>
-    <row r="51" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="37">
@@ -4845,7 +4723,7 @@
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
     </row>
-    <row r="52" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="37">
@@ -4890,7 +4768,7 @@
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
     </row>
-    <row r="53" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="37">
@@ -4935,7 +4813,7 @@
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
     </row>
-    <row r="54" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="37">
@@ -4980,7 +4858,7 @@
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
     </row>
-    <row r="55" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="37">
@@ -5025,7 +4903,7 @@
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
     </row>
-    <row r="56" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="37">
@@ -5070,7 +4948,7 @@
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
     </row>
-    <row r="57" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="37">
@@ -5115,7 +4993,7 @@
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
     </row>
-    <row r="58" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="37">
@@ -5160,7 +5038,7 @@
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
     </row>
-    <row r="59" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="37">
@@ -5178,8 +5056,8 @@
       <c r="G59" s="2"/>
       <c r="H59" s="35"/>
       <c r="I59" s="1"/>
-      <c r="J59" s="77"/>
-      <c r="K59" s="77"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -5205,7 +5083,7 @@
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
     </row>
-    <row r="60" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="37">
@@ -5223,8 +5101,8 @@
       <c r="G60" s="2"/>
       <c r="H60" s="35"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="77"/>
-      <c r="K60" s="77"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
@@ -5250,7 +5128,7 @@
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
     </row>
-    <row r="61" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="37">
@@ -5268,8 +5146,8 @@
       <c r="G61" s="2"/>
       <c r="H61" s="35"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="77"/>
-      <c r="K61" s="77"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -5295,7 +5173,7 @@
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
     </row>
-    <row r="62" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="37">
@@ -5340,7 +5218,7 @@
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
     </row>
-    <row r="63" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="37">
@@ -5385,7 +5263,7 @@
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
     </row>
-    <row r="64" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="37">
@@ -5430,7 +5308,7 @@
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
     </row>
-    <row r="65" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="37">
@@ -5475,7 +5353,7 @@
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
     </row>
-    <row r="66" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="37">
@@ -5520,7 +5398,7 @@
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
     </row>
-    <row r="67" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="37">
@@ -5565,7 +5443,7 @@
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
     </row>
-    <row r="68" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="37">
@@ -5610,7 +5488,7 @@
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
     </row>
-    <row r="69" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="37">
@@ -5655,7 +5533,7 @@
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
     </row>
-    <row r="70" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="37">
@@ -5700,7 +5578,7 @@
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
     </row>
-    <row r="71" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="37">
@@ -5745,7 +5623,7 @@
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
     </row>
-    <row r="72" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="37">
@@ -5790,7 +5668,7 @@
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
     </row>
-    <row r="73" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="37">
@@ -5835,7 +5713,7 @@
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
     </row>
-    <row r="74" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="37">
@@ -5880,7 +5758,7 @@
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
     </row>
-    <row r="75" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="37">
@@ -5925,7 +5803,7 @@
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
     </row>
-    <row r="76" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="37">
@@ -5970,7 +5848,7 @@
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
     </row>
-    <row r="77" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="37">
@@ -6015,7 +5893,7 @@
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
     </row>
-    <row r="78" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="37">
@@ -6060,7 +5938,7 @@
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
     </row>
-    <row r="79" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="37">
@@ -6105,7 +5983,7 @@
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
     </row>
-    <row r="80" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="37">
@@ -6150,7 +6028,7 @@
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
     </row>
-    <row r="81" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="37">
@@ -6195,7 +6073,7 @@
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
     </row>
-    <row r="82" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="37">
@@ -6240,7 +6118,7 @@
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
     </row>
-    <row r="83" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="37">
@@ -6285,7 +6163,7 @@
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
     </row>
-    <row r="84" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="37">
@@ -6330,7 +6208,7 @@
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
     </row>
-    <row r="85" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="37">
@@ -6375,7 +6253,7 @@
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
     </row>
-    <row r="86" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="37">
@@ -6420,7 +6298,7 @@
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
     </row>
-    <row r="87" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="37">
@@ -6465,7 +6343,7 @@
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
     </row>
-    <row r="88" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="37">
@@ -6510,7 +6388,7 @@
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
     </row>
-    <row r="89" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="37">
@@ -6555,7 +6433,7 @@
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
     </row>
-    <row r="90" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="37">
@@ -6600,7 +6478,7 @@
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
     </row>
-    <row r="91" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="37">
@@ -6645,7 +6523,7 @@
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
     </row>
-    <row r="92" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="37">
@@ -6690,7 +6568,7 @@
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
     </row>
-    <row r="93" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="37">
@@ -6735,7 +6613,7 @@
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
     </row>
-    <row r="94" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="37">
@@ -6780,7 +6658,7 @@
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
     </row>
-    <row r="95" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="37">
@@ -6825,7 +6703,7 @@
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
     </row>
-    <row r="96" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="37">
@@ -6870,7 +6748,7 @@
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
     </row>
-    <row r="97" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="37">
@@ -6915,7 +6793,7 @@
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
     </row>
-    <row r="98" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="37">
@@ -6960,7 +6838,7 @@
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
     </row>
-    <row r="99" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="37">
@@ -7005,7 +6883,7 @@
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
     </row>
-    <row r="100" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="37">
@@ -7050,7 +6928,7 @@
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
     </row>
-    <row r="101" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="37">
@@ -7095,7 +6973,7 @@
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
     </row>
-    <row r="102" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="37">
@@ -7140,7 +7018,7 @@
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
     </row>
-    <row r="103" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="37">
@@ -7185,7 +7063,7 @@
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
     </row>
-    <row r="104" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="37">
@@ -7230,7 +7108,7 @@
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
     </row>
-    <row r="105" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="37">
@@ -7275,7 +7153,7 @@
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
     </row>
-    <row r="106" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="37">
@@ -7320,7 +7198,7 @@
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
     </row>
-    <row r="107" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="37">
@@ -7365,7 +7243,7 @@
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
     </row>
-    <row r="108" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="37">
@@ -7410,7 +7288,7 @@
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
     </row>
-    <row r="109" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="37">
@@ -7455,7 +7333,7 @@
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
     </row>
-    <row r="110" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="37">
@@ -7500,7 +7378,7 @@
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
     </row>
-    <row r="111" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="37">
@@ -7545,7 +7423,7 @@
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
     </row>
-    <row r="112" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="37">
@@ -7590,7 +7468,7 @@
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
     </row>
-    <row r="113" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="37">
@@ -7635,7 +7513,7 @@
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
     </row>
-    <row r="114" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="37">
@@ -7680,7 +7558,7 @@
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
     </row>
-    <row r="115" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="37">
@@ -7725,7 +7603,7 @@
       <c r="AH115" s="1"/>
       <c r="AI115" s="1"/>
     </row>
-    <row r="116" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="37">
@@ -7770,7 +7648,7 @@
       <c r="AH116" s="1"/>
       <c r="AI116" s="1"/>
     </row>
-    <row r="117" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="37">
@@ -7815,7 +7693,7 @@
       <c r="AH117" s="1"/>
       <c r="AI117" s="1"/>
     </row>
-    <row r="118" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="37">
@@ -7860,7 +7738,7 @@
       <c r="AH118" s="1"/>
       <c r="AI118" s="1"/>
     </row>
-    <row r="119" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="37">
@@ -7905,7 +7783,7 @@
       <c r="AH119" s="1"/>
       <c r="AI119" s="1"/>
     </row>
-    <row r="120" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="37">
@@ -7950,7 +7828,7 @@
       <c r="AH120" s="1"/>
       <c r="AI120" s="1"/>
     </row>
-    <row r="121" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="37">
@@ -7995,15 +7873,15 @@
       <c r="AH121" s="1"/>
       <c r="AI121" s="1"/>
     </row>
-    <row r="122" spans="1:35" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:35" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="38"/>
-      <c r="D122" s="81"/>
+      <c r="D122" s="60"/>
       <c r="E122" s="39"/>
       <c r="F122" s="40"/>
       <c r="G122" s="39"/>
-      <c r="H122" s="79"/>
+      <c r="H122" s="58"/>
       <c r="I122" s="9"/>
       <c r="J122" s="54"/>
       <c r="K122" s="29"/>
@@ -8032,7 +7910,7 @@
       <c r="AH122" s="1"/>
       <c r="AI122" s="1"/>
     </row>
-    <row r="123" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -8069,7 +7947,7 @@
       <c r="AH123" s="1"/>
       <c r="AI123" s="1"/>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -8106,7 +7984,7 @@
       <c r="AH124" s="1"/>
       <c r="AI124" s="1"/>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -8143,7 +8021,7 @@
       <c r="AH125" s="1"/>
       <c r="AI125" s="1"/>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -8180,7 +8058,7 @@
       <c r="AH126" s="1"/>
       <c r="AI126" s="1"/>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -8217,7 +8095,7 @@
       <c r="AH127" s="1"/>
       <c r="AI127" s="1"/>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -8254,7 +8132,7 @@
       <c r="AH128" s="1"/>
       <c r="AI128" s="1"/>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8291,7 +8169,7 @@
       <c r="AH129" s="1"/>
       <c r="AI129" s="1"/>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8328,7 +8206,7 @@
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -8365,7 +8243,7 @@
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -8402,7 +8280,7 @@
       <c r="AH132" s="1"/>
       <c r="AI132" s="1"/>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -8439,7 +8317,7 @@
       <c r="AH133" s="1"/>
       <c r="AI133" s="1"/>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -8476,7 +8354,7 @@
       <c r="AH134" s="1"/>
       <c r="AI134" s="1"/>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -8513,7 +8391,7 @@
       <c r="AH135" s="1"/>
       <c r="AI135" s="1"/>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -8550,7 +8428,7 @@
       <c r="AH136" s="1"/>
       <c r="AI136" s="1"/>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -8587,7 +8465,7 @@
       <c r="AH137" s="1"/>
       <c r="AI137" s="1"/>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -8624,7 +8502,7 @@
       <c r="AH138" s="1"/>
       <c r="AI138" s="1"/>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -8688,19 +8566,19 @@
   <conditionalFormatting sqref="J10:J36">
     <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K10">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K10">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D123" xr:uid="{F28DF3C7-C5D8-43E9-AFD8-1CCDDB0B7277}">
@@ -8727,29 +8605,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11843C76-C743-4599-8199-91D60832CD73}">
   <dimension ref="A1:AI139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" customWidth="1"/>
-    <col min="5" max="5" width="88.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
-    <col min="11" max="11" width="38.42578125" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" customWidth="1"/>
-    <col min="14" max="14" width="22.7109375" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" customWidth="1"/>
-    <col min="16" max="16" width="2.5703125" customWidth="1"/>
-    <col min="20" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" customWidth="1"/>
+    <col min="5" max="5" width="88.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="11" max="11" width="38.44140625" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" customWidth="1"/>
+    <col min="13" max="13" width="15.88671875" customWidth="1"/>
+    <col min="14" max="14" width="22.6640625" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" customWidth="1"/>
+    <col min="16" max="16" width="2.5546875" customWidth="1"/>
+    <col min="20" max="21" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="58"/>
-      <c r="B1" s="58"/>
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A1" s="79"/>
+      <c r="B1" s="79"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -8783,22 +8661,22 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="68" t="s">
+    <row r="2" spans="1:35" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="70" t="s">
-        <v>137</v>
-      </c>
-      <c r="K2" s="70"/>
+      <c r="J2" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="82"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -8824,18 +8702,18 @@
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -8861,18 +8739,18 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -8898,18 +8776,18 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -8935,18 +8813,18 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
     </row>
-    <row r="6" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+    <row r="6" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -8972,7 +8850,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="55"/>
@@ -9009,7 +8887,7 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -9044,7 +8922,7 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="31" t="s">
@@ -9097,30 +8975,22 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="34">
-        <v>46055</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-60.31</v>
-      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="80"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="82" t="s">
+      <c r="J10" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="89">
+      <c r="K10" s="68">
         <f>SUMIF($D$10:$D$117,J10,$F$10:$F$117)</f>
-        <v>5147.3000000000011</v>
+        <v>0</v>
       </c>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
@@ -9147,36 +9017,28 @@
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="36">
-        <v>46055</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-173.88</v>
-      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="2"/>
       <c r="H11" s="35"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="82" t="s">
+      <c r="J11" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="88">
+      <c r="K11" s="67">
         <f>SUMIF($D$10:$D$117,J11,$F$10:$F$117)</f>
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="L11" s="41"/>
-      <c r="M11" s="72" t="s">
+      <c r="M11" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="72"/>
+      <c r="N11" s="84"/>
       <c r="O11" s="42"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -9199,34 +9061,26 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
     </row>
-    <row r="12" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="37">
-        <v>46055</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="5">
-        <v>-76.89</v>
-      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="2"/>
       <c r="H12" s="35"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="83" t="s">
+      <c r="J12" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="66">
         <f t="shared" ref="K12:K36" si="0">SUMIF($D$10:$D$117,J12,$F$10:$F$117)</f>
-        <v>-436.91</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="73"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
       <c r="O12" s="25"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -9249,30 +9103,22 @@
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="37">
-        <v>46055</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="7">
-        <v>-142.07</v>
-      </c>
+      <c r="C13" s="37"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="2"/>
       <c r="H13" s="35"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="83" t="s">
+      <c r="J13" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="87">
+      <c r="K13" s="66">
         <f t="shared" si="0"/>
-        <v>-83.21</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="16" t="s">
@@ -9280,7 +9126,7 @@
       </c>
       <c r="N13" s="17">
         <f>SUMIF(D10:D117,"Revenue",F10:F117)</f>
-        <v>5147.3000000000011</v>
+        <v>0</v>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="1"/>
@@ -9304,28 +9150,20 @@
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
     </row>
-    <row r="14" spans="1:35" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="37">
-        <v>46055</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="7">
-        <v>119.13</v>
-      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="2"/>
       <c r="H14" s="35"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="83" t="s">
+      <c r="J14" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="87">
+      <c r="K14" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9335,7 +9173,7 @@
       </c>
       <c r="N14" s="56">
         <f>SUMIF(D10:D118,"&lt;&gt;Revenue",F10:F118)</f>
-        <v>-8240.1299999999992</v>
+        <v>0</v>
       </c>
       <c r="O14" s="25"/>
       <c r="P14" s="1"/>
@@ -9359,30 +9197,22 @@
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
     </row>
-    <row r="15" spans="1:35" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" ht="19.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="37">
-        <v>46056</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="7">
-        <v>135.38</v>
-      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="2"/>
       <c r="H15" s="35"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="83" t="s">
+      <c r="J15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="87">
+      <c r="K15" s="66">
         <f t="shared" si="0"/>
-        <v>-92.58</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="18" t="s">
@@ -9390,7 +9220,7 @@
       </c>
       <c r="N15" s="19">
         <f>N13+(N14)</f>
-        <v>-3092.8299999999981</v>
+        <v>0</v>
       </c>
       <c r="O15" s="25"/>
       <c r="P15" s="1"/>
@@ -9414,28 +9244,20 @@
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="37">
-        <v>46056</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="7">
-        <v>146.21</v>
-      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="2"/>
       <c r="H16" s="35"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="83" t="s">
-        <v>136</v>
-      </c>
-      <c r="K16" s="87">
+      <c r="J16" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9464,36 +9286,28 @@
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="1:35" ht="20.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" ht="20.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="37">
-        <v>46056</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="7">
-        <v>140.5</v>
-      </c>
+      <c r="C17" s="37"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="2"/>
       <c r="H17" s="35"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="83" t="s">
+      <c r="J17" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="87">
+      <c r="K17" s="66">
         <f t="shared" si="0"/>
-        <v>119.13</v>
-      </c>
-      <c r="L17" s="85"/>
-      <c r="M17" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="L17" s="64"/>
+      <c r="M17" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="N17" s="74"/>
+      <c r="N17" s="86"/>
       <c r="O17" s="27"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -9516,34 +9330,26 @@
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
     </row>
-    <row r="18" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="37">
-        <v>46056</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F18" s="7">
-        <v>-1200</v>
-      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="2"/>
       <c r="H18" s="35"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="83" t="s">
+      <c r="J18" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="87">
+      <c r="K18" s="66">
         <f t="shared" si="0"/>
-        <v>-1300</v>
-      </c>
-      <c r="L18" s="86"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="75"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="65"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
       <c r="O18" s="28"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -9566,36 +9372,28 @@
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
     </row>
-    <row r="19" spans="1:35" ht="20.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" ht="20.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="37">
-        <v>46056</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="7">
-        <v>-1300</v>
-      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="2"/>
       <c r="H19" s="35"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="83" t="s">
+      <c r="J19" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L19" s="1"/>
-      <c r="M19" s="67" t="s">
+      <c r="M19" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="N19" s="76" t="s">
+      <c r="N19" s="88" t="s">
         <v>16</v>
       </c>
       <c r="O19" s="25"/>
@@ -9620,34 +9418,26 @@
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
     </row>
-    <row r="20" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="37">
-        <v>46056</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F20" s="7">
-        <v>-400</v>
-      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="2"/>
       <c r="H20" s="35"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="83" t="s">
+      <c r="J20" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="87">
+      <c r="K20" s="66">
         <f t="shared" si="0"/>
-        <v>-322.56</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="76"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="88"/>
       <c r="O20" s="25"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -9670,37 +9460,29 @@
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
     </row>
-    <row r="21" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="37">
-        <v>46057</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="7">
-        <v>-1300</v>
-      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="2"/>
       <c r="H21" s="35"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="83" t="s">
+      <c r="J21" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="87">
+      <c r="K21" s="66">
         <f t="shared" si="0"/>
-        <v>-25.07</v>
+        <v>0</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="65">
+      <c r="M21" s="76">
         <f>COUNTIF($D$11:$D$122, "Subscriptions")</f>
-        <v>1</v>
-      </c>
-      <c r="N21" s="66">
+        <v>0</v>
+      </c>
+      <c r="N21" s="77">
         <f>COUNTIF($D$11:$D$122, "Restaurant")</f>
         <v>0</v>
       </c>
@@ -9726,34 +9508,26 @@
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
     </row>
-    <row r="22" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="37">
-        <v>46057</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="7">
-        <v>136.4</v>
-      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="2"/>
       <c r="H22" s="35"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="83" t="s">
+      <c r="J22" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="K22" s="87">
+      <c r="K22" s="66">
         <f t="shared" si="0"/>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="66"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="77"/>
       <c r="O22" s="25"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -9776,28 +9550,20 @@
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
     </row>
-    <row r="23" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="37">
-        <v>46057</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F23" s="7">
-        <v>-100</v>
-      </c>
+      <c r="C23" s="37"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="2"/>
       <c r="H23" s="35"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="83" t="s">
+      <c r="J23" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="K23" s="87">
+      <c r="K23" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9826,36 +9592,28 @@
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
     </row>
-    <row r="24" spans="1:35" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="37">
-        <v>46058</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F24" s="7">
-        <v>-35.909999999999997</v>
-      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="2"/>
       <c r="H24" s="35"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="84" t="s">
+      <c r="J24" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="K24" s="87">
+      <c r="K24" s="66">
         <f t="shared" si="0"/>
-        <v>-1721.55</v>
+        <v>0</v>
       </c>
       <c r="L24" s="20"/>
-      <c r="M24" s="67" t="s">
+      <c r="M24" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="67" t="s">
+      <c r="N24" s="78" t="s">
         <v>20</v>
       </c>
       <c r="O24" s="25"/>
@@ -9880,34 +9638,26 @@
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
     </row>
-    <row r="25" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="37">
-        <v>46058</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="7">
-        <v>0.01</v>
-      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="2"/>
       <c r="H25" s="35"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="84" t="s">
+      <c r="J25" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="87">
+      <c r="K25" s="66">
         <f t="shared" si="0"/>
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="L25" s="20"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
+      <c r="M25" s="78"/>
+      <c r="N25" s="78"/>
       <c r="O25" s="25"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -9930,37 +9680,29 @@
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
     </row>
-    <row r="26" spans="1:35" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" ht="18.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="37">
-        <v>46059</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="7">
-        <v>98.84</v>
-      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="2"/>
       <c r="H26" s="35"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="84" t="s">
+      <c r="J26" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="87">
+      <c r="K26" s="66">
         <f t="shared" si="0"/>
-        <v>-134.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="L26" s="20"/>
-      <c r="M26" s="66">
+      <c r="M26" s="77">
         <f>COUNTIF($D$11:$D$122, "Gas")</f>
         <v>0</v>
       </c>
-      <c r="N26" s="66">
+      <c r="N26" s="77">
         <f>COUNTIF($D$11:$D$122, "Savings")</f>
         <v>0</v>
       </c>
@@ -9986,34 +9728,26 @@
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
     </row>
-    <row r="27" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="37">
-        <v>46059</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="7">
-        <v>-128.49</v>
-      </c>
+      <c r="C27" s="37"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="2"/>
       <c r="H27" s="35"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="84" t="s">
+      <c r="J27" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="87">
+      <c r="K27" s="66">
         <f t="shared" si="0"/>
-        <v>-53.32</v>
+        <v>0</v>
       </c>
       <c r="L27" s="20"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
+      <c r="M27" s="77"/>
+      <c r="N27" s="77"/>
       <c r="O27" s="25"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -10036,34 +9770,26 @@
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
     </row>
-    <row r="28" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="37">
-        <v>46062</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28" s="7">
-        <v>238.49</v>
-      </c>
+      <c r="C28" s="37"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="2"/>
       <c r="H28" s="35"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="83" t="s">
+      <c r="J28" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="K28" s="87">
+      <c r="K28" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L28" s="20"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
+      <c r="M28" s="77"/>
+      <c r="N28" s="77"/>
       <c r="O28" s="25"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -10086,34 +9812,26 @@
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
     </row>
-    <row r="29" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="37">
-        <v>46062</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" s="7">
-        <v>-83.21</v>
-      </c>
+      <c r="C29" s="37"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="2"/>
       <c r="H29" s="35"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="87">
+      <c r="K29" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L29" s="78"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
       <c r="O29" s="25"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -10136,34 +9854,26 @@
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
     </row>
-    <row r="30" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="37">
-        <v>46063</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="7">
-        <v>712.01</v>
-      </c>
+      <c r="C30" s="37"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
       <c r="G30" s="2"/>
       <c r="H30" s="35"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="83" t="s">
+      <c r="J30" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="K30" s="87">
+      <c r="K30" s="66">
         <f t="shared" si="0"/>
-        <v>-163.75</v>
-      </c>
-      <c r="L30" s="78"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="77"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="20"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
       <c r="O30" s="25"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -10186,34 +9896,26 @@
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
     </row>
-    <row r="31" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="37">
-        <v>46063</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="7">
-        <v>-54.91</v>
-      </c>
+      <c r="C31" s="37"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="2"/>
       <c r="H31" s="35"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="83" t="s">
+      <c r="J31" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="87">
+      <c r="K31" s="66">
         <f t="shared" si="0"/>
-        <v>-435</v>
-      </c>
-      <c r="L31" s="78"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="77"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="20"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
       <c r="O31" s="25"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -10236,34 +9938,26 @@
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
     </row>
-    <row r="32" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="37">
-        <v>46064</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="7">
-        <v>-30.32</v>
-      </c>
+      <c r="C32" s="37"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="2"/>
       <c r="H32" s="35"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="83" t="s">
+      <c r="J32" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="87">
+      <c r="K32" s="66">
         <f t="shared" si="0"/>
-        <v>-1700</v>
-      </c>
-      <c r="L32" s="78"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
       <c r="O32" s="25"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -10286,34 +9980,26 @@
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
     </row>
-    <row r="33" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="37">
-        <v>46064</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="7">
-        <v>-158.96</v>
-      </c>
+      <c r="C33" s="37"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="2"/>
       <c r="H33" s="35"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="83" t="s">
+      <c r="J33" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="K33" s="87">
+      <c r="K33" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L33" s="78"/>
-      <c r="M33" s="77"/>
-      <c r="N33" s="77"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="25"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -10336,34 +10022,26 @@
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
     </row>
-    <row r="34" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="37">
-        <v>46065</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="7">
-        <v>216.33</v>
-      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="2"/>
       <c r="H34" s="35"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="K34" s="87">
+      <c r="K34" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L34" s="78"/>
-      <c r="M34" s="77"/>
-      <c r="N34" s="77"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
       <c r="O34" s="25"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -10386,34 +10064,26 @@
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
     </row>
-    <row r="35" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="37">
-        <v>46065</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F35" s="7">
-        <v>-436.91</v>
-      </c>
+      <c r="C35" s="37"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
       <c r="G35" s="2"/>
       <c r="H35" s="35"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="83" t="s">
+      <c r="J35" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="87">
+      <c r="K35" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L35" s="78"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
       <c r="O35" s="25"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -10436,34 +10106,26 @@
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
     </row>
-    <row r="36" spans="1:35" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="37">
-        <v>46065</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F36" s="7">
-        <v>-593.42999999999995</v>
-      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="2"/>
       <c r="H36" s="35"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="83" t="s">
+      <c r="J36" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="K36" s="87">
+      <c r="K36" s="66">
         <f t="shared" si="0"/>
-        <v>-299.99</v>
-      </c>
-      <c r="L36" s="78"/>
-      <c r="M36" s="77"/>
-      <c r="N36" s="77"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="20"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
       <c r="O36" s="25"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -10486,21 +10148,13 @@
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
     </row>
-    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="37">
-        <v>46066</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F37" s="7">
-        <v>308.62</v>
-      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
       <c r="G37" s="2"/>
       <c r="H37" s="35"/>
       <c r="I37" s="1"/>
@@ -10531,30 +10185,22 @@
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
     </row>
-    <row r="38" spans="1:35" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="37">
-        <v>46066</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="7">
-        <v>268.31</v>
-      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
       <c r="G38" s="2"/>
       <c r="H38" s="35"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="62"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="73"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
@@ -10576,30 +10222,22 @@
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
     </row>
-    <row r="39" spans="1:35" ht="23.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="37">
-        <v>46066</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F39" s="7">
-        <v>271.02</v>
-      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
       <c r="G39" s="2"/>
       <c r="H39" s="35"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="63"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="64"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="74"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="75"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
@@ -10621,21 +10259,13 @@
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
     </row>
-    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="37">
-        <v>46066</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="7">
-        <v>-10</v>
-      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7"/>
       <c r="G40" s="2"/>
       <c r="H40" s="35"/>
       <c r="I40" s="1"/>
@@ -10666,21 +10296,13 @@
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
     </row>
-    <row r="41" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="37">
-        <v>46066</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F41" s="7">
-        <v>-14.84</v>
-      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7"/>
       <c r="G41" s="2"/>
       <c r="H41" s="35"/>
       <c r="I41" s="1"/>
@@ -10711,21 +10333,13 @@
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
     </row>
-    <row r="42" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="37">
-        <v>46066</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F42" s="7">
-        <v>-25.07</v>
-      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="2"/>
       <c r="H42" s="35"/>
       <c r="I42" s="1"/>
@@ -10756,21 +10370,13 @@
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
     </row>
-    <row r="43" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
-      <c r="C43" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F43" s="7">
-        <v>-20</v>
-      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="7"/>
       <c r="G43" s="2"/>
       <c r="H43" s="35"/>
       <c r="I43" s="1"/>
@@ -10801,21 +10407,13 @@
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
     </row>
-    <row r="44" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
-      <c r="C44" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F44" s="7">
-        <v>182.85</v>
-      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7"/>
       <c r="G44" s="2"/>
       <c r="H44" s="35"/>
       <c r="I44" s="1"/>
@@ -10846,21 +10444,13 @@
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
     </row>
-    <row r="45" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F45" s="7">
-        <v>338.16</v>
-      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
       <c r="G45" s="2"/>
       <c r="H45" s="35"/>
       <c r="I45" s="1"/>
@@ -10893,21 +10483,13 @@
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
     </row>
-    <row r="46" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
-      <c r="C46" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F46" s="7">
-        <v>178.78</v>
-      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
       <c r="G46" s="2"/>
       <c r="H46" s="35"/>
       <c r="I46" s="1"/>
@@ -10938,21 +10520,13 @@
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
     </row>
-    <row r="47" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F47" s="7">
-        <v>-0.38</v>
-      </c>
+      <c r="C47" s="37"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
       <c r="G47" s="2"/>
       <c r="H47" s="35"/>
       <c r="I47" s="1"/>
@@ -10983,21 +10557,13 @@
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
     </row>
-    <row r="48" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="7">
-        <v>-38.1</v>
-      </c>
+      <c r="C48" s="37"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
       <c r="G48" s="2"/>
       <c r="H48" s="35"/>
       <c r="I48" s="1"/>
@@ -11028,21 +10594,13 @@
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
     </row>
-    <row r="49" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F49" s="7">
-        <v>210.86</v>
-      </c>
+      <c r="C49" s="37"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
       <c r="G49" s="2"/>
       <c r="H49" s="35"/>
       <c r="I49" s="1"/>
@@ -11073,21 +10631,13 @@
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
     </row>
-    <row r="50" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="7">
-        <v>42.95</v>
-      </c>
+      <c r="C50" s="37"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7"/>
       <c r="G50" s="2"/>
       <c r="H50" s="35"/>
       <c r="I50" s="1"/>
@@ -11118,21 +10668,13 @@
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
     </row>
-    <row r="51" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F51" s="7">
-        <v>140.80000000000001</v>
-      </c>
+      <c r="C51" s="37"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
       <c r="G51" s="2"/>
       <c r="H51" s="35"/>
       <c r="I51" s="1"/>
@@ -11163,21 +10705,13 @@
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
     </row>
-    <row r="52" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F52" s="7">
-        <v>-163.75</v>
-      </c>
+      <c r="C52" s="37"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
       <c r="G52" s="2"/>
       <c r="H52" s="35"/>
       <c r="I52" s="1"/>
@@ -11208,21 +10742,13 @@
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
     </row>
-    <row r="53" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
-      <c r="C53" s="37">
-        <v>46067</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F53" s="7">
-        <v>-25.4</v>
-      </c>
+      <c r="C53" s="37"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="7"/>
       <c r="G53" s="2"/>
       <c r="H53" s="35"/>
       <c r="I53" s="1"/>
@@ -11253,21 +10779,13 @@
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
     </row>
-    <row r="54" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
-      <c r="C54" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F54" s="7">
-        <v>163.28</v>
-      </c>
+      <c r="C54" s="37"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7"/>
       <c r="G54" s="2"/>
       <c r="H54" s="35"/>
       <c r="I54" s="1"/>
@@ -11298,21 +10816,13 @@
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
     </row>
-    <row r="55" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="7">
-        <v>-30</v>
-      </c>
+      <c r="C55" s="37"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="7"/>
       <c r="G55" s="2"/>
       <c r="H55" s="35"/>
       <c r="I55" s="1"/>
@@ -11343,21 +10853,13 @@
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
     </row>
-    <row r="56" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F56" s="7">
-        <v>-12</v>
-      </c>
+      <c r="C56" s="37"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7"/>
       <c r="G56" s="2"/>
       <c r="H56" s="35"/>
       <c r="I56" s="1"/>
@@ -11388,21 +10890,13 @@
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
     </row>
-    <row r="57" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F57" s="7">
-        <v>-92.58</v>
-      </c>
+      <c r="C57" s="37"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7"/>
       <c r="G57" s="2"/>
       <c r="H57" s="35"/>
       <c r="I57" s="1"/>
@@ -11433,21 +10927,13 @@
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
     </row>
-    <row r="58" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F58" s="7">
-        <v>-224.41</v>
-      </c>
+      <c r="C58" s="37"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="7"/>
       <c r="G58" s="2"/>
       <c r="H58" s="35"/>
       <c r="I58" s="1"/>
@@ -11478,21 +10964,13 @@
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
     </row>
-    <row r="59" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F59" s="7">
-        <v>638.04999999999995</v>
-      </c>
+      <c r="C59" s="37"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7"/>
       <c r="G59" s="2"/>
       <c r="H59" s="35"/>
       <c r="I59" s="1"/>
@@ -11523,21 +11001,13 @@
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
     </row>
-    <row r="60" spans="1:35" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:35" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F60" s="7">
-        <v>146.21</v>
-      </c>
+      <c r="C60" s="37"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="7"/>
       <c r="G60" s="2"/>
       <c r="H60" s="35"/>
       <c r="I60" s="1"/>
@@ -11568,25 +11038,17 @@
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
     </row>
-    <row r="61" spans="1:35" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F61" s="7">
-        <v>-5</v>
-      </c>
+      <c r="C61" s="37"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="7"/>
       <c r="G61" s="2"/>
       <c r="H61" s="35"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="90"/>
+      <c r="J61" s="69"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -11613,21 +11075,13 @@
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
     </row>
-    <row r="62" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F62" s="7">
-        <v>-3</v>
-      </c>
+      <c r="C62" s="37"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="7"/>
       <c r="G62" s="2"/>
       <c r="H62" s="35"/>
       <c r="I62" s="1"/>
@@ -11658,21 +11112,13 @@
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
     </row>
-    <row r="63" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F63" s="7">
-        <v>102.81</v>
-      </c>
+      <c r="C63" s="37"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7"/>
       <c r="G63" s="2"/>
       <c r="H63" s="35"/>
       <c r="I63" s="1"/>
@@ -11703,21 +11149,13 @@
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
     </row>
-    <row r="64" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F64" s="7">
-        <v>189.63</v>
-      </c>
+      <c r="C64" s="37"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="7"/>
       <c r="G64" s="2"/>
       <c r="H64" s="35"/>
       <c r="I64" s="1"/>
@@ -11748,21 +11186,13 @@
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
     </row>
-    <row r="65" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F65" s="7">
-        <v>-30.67</v>
-      </c>
+      <c r="C65" s="37"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="7"/>
       <c r="G65" s="2"/>
       <c r="H65" s="35"/>
       <c r="I65" s="1"/>
@@ -11793,21 +11223,13 @@
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
     </row>
-    <row r="66" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="37">
-        <v>46070</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F66" s="7">
-        <v>-7.66</v>
-      </c>
+      <c r="C66" s="37"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="7"/>
       <c r="G66" s="2"/>
       <c r="H66" s="35"/>
       <c r="I66" s="1"/>
@@ -11838,21 +11260,13 @@
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
     </row>
-    <row r="67" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="37">
-        <v>46071</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F67" s="7">
-        <v>140.80000000000001</v>
-      </c>
+      <c r="C67" s="37"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="2"/>
       <c r="H67" s="35"/>
       <c r="I67" s="1"/>
@@ -11883,21 +11297,13 @@
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
     </row>
-    <row r="68" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="37">
-        <v>46071</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F68" s="7">
-        <v>-12</v>
-      </c>
+      <c r="C68" s="37"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="7"/>
       <c r="G68" s="2"/>
       <c r="H68" s="35"/>
       <c r="I68" s="1"/>
@@ -11928,21 +11334,13 @@
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
     </row>
-    <row r="69" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="37">
-        <v>46071</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F69" s="7">
-        <v>-299.99</v>
-      </c>
+      <c r="C69" s="37"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="7"/>
       <c r="G69" s="2"/>
       <c r="H69" s="35"/>
       <c r="I69" s="1"/>
@@ -11973,21 +11371,13 @@
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
     </row>
-    <row r="70" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="37">
-        <v>46071</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F70" s="7">
-        <v>-538.63</v>
-      </c>
+      <c r="C70" s="37"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="2"/>
       <c r="H70" s="35"/>
       <c r="I70" s="1"/>
@@ -12018,21 +11408,13 @@
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
     </row>
-    <row r="71" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="37">
-        <v>46071</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F71" s="7">
-        <v>-95.49</v>
-      </c>
+      <c r="C71" s="37"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="2"/>
       <c r="H71" s="35"/>
       <c r="I71" s="1"/>
@@ -12063,21 +11445,13 @@
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
     </row>
-    <row r="72" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="37">
-        <v>46072</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F72" s="7">
-        <v>-435</v>
-      </c>
+      <c r="C72" s="37"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="7"/>
       <c r="G72" s="2"/>
       <c r="H72" s="35"/>
       <c r="I72" s="1"/>
@@ -12108,7 +11482,7 @@
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
     </row>
-    <row r="73" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="37"/>
@@ -12145,7 +11519,7 @@
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
     </row>
-    <row r="74" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="37"/>
@@ -12182,7 +11556,7 @@
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
     </row>
-    <row r="75" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="37"/>
@@ -12219,7 +11593,7 @@
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
     </row>
-    <row r="76" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="37"/>
@@ -12256,7 +11630,7 @@
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
     </row>
-    <row r="77" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="37"/>
@@ -12293,7 +11667,7 @@
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
     </row>
-    <row r="78" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="37"/>
@@ -12330,7 +11704,7 @@
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
     </row>
-    <row r="79" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="37"/>
@@ -12367,7 +11741,7 @@
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
     </row>
-    <row r="80" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="37"/>
@@ -12404,7 +11778,7 @@
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
     </row>
-    <row r="81" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="37"/>
@@ -12441,7 +11815,7 @@
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
     </row>
-    <row r="82" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="37"/>
@@ -12478,7 +11852,7 @@
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
     </row>
-    <row r="83" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="37"/>
@@ -12515,7 +11889,7 @@
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
     </row>
-    <row r="84" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="37"/>
@@ -12552,7 +11926,7 @@
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
     </row>
-    <row r="85" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="37"/>
@@ -12589,7 +11963,7 @@
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
     </row>
-    <row r="86" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="37"/>
@@ -12626,7 +12000,7 @@
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
     </row>
-    <row r="87" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="37"/>
@@ -12663,7 +12037,7 @@
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
     </row>
-    <row r="88" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="37"/>
@@ -12700,7 +12074,7 @@
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
     </row>
-    <row r="89" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="37"/>
@@ -12737,7 +12111,7 @@
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
     </row>
-    <row r="90" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="37"/>
@@ -12774,7 +12148,7 @@
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
     </row>
-    <row r="91" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="37"/>
@@ -12811,7 +12185,7 @@
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
     </row>
-    <row r="92" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="37"/>
@@ -12848,7 +12222,7 @@
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
     </row>
-    <row r="93" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="37"/>
@@ -12885,7 +12259,7 @@
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
     </row>
-    <row r="94" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="37"/>
@@ -12922,7 +12296,7 @@
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
     </row>
-    <row r="95" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="37"/>
@@ -12959,7 +12333,7 @@
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
     </row>
-    <row r="96" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="37"/>
@@ -12996,7 +12370,7 @@
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
     </row>
-    <row r="97" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="37"/>
@@ -13033,7 +12407,7 @@
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
     </row>
-    <row r="98" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="37"/>
@@ -13070,7 +12444,7 @@
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
     </row>
-    <row r="99" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="37"/>
@@ -13107,7 +12481,7 @@
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
     </row>
-    <row r="100" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="37"/>
@@ -13144,7 +12518,7 @@
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
     </row>
-    <row r="101" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="37"/>
@@ -13181,7 +12555,7 @@
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
     </row>
-    <row r="102" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="37"/>
@@ -13218,7 +12592,7 @@
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
     </row>
-    <row r="103" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="37"/>
@@ -13255,7 +12629,7 @@
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
     </row>
-    <row r="104" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="37"/>
@@ -13292,7 +12666,7 @@
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
     </row>
-    <row r="105" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="37"/>
@@ -13329,7 +12703,7 @@
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
     </row>
-    <row r="106" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="37"/>
@@ -13366,7 +12740,7 @@
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
     </row>
-    <row r="107" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="37"/>
@@ -13403,7 +12777,7 @@
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
     </row>
-    <row r="108" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="37"/>
@@ -13440,7 +12814,7 @@
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
     </row>
-    <row r="109" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="37"/>
@@ -13477,7 +12851,7 @@
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
     </row>
-    <row r="110" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="37"/>
@@ -13514,7 +12888,7 @@
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
     </row>
-    <row r="111" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="37"/>
@@ -13551,7 +12925,7 @@
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
     </row>
-    <row r="112" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="37"/>
@@ -13588,7 +12962,7 @@
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
     </row>
-    <row r="113" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="37"/>
@@ -13625,7 +12999,7 @@
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
     </row>
-    <row r="114" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="37"/>
@@ -13662,7 +13036,7 @@
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
     </row>
-    <row r="115" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="37"/>
@@ -13699,7 +13073,7 @@
       <c r="AH115" s="1"/>
       <c r="AI115" s="1"/>
     </row>
-    <row r="116" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="37"/>
@@ -13736,7 +13110,7 @@
       <c r="AH116" s="1"/>
       <c r="AI116" s="1"/>
     </row>
-    <row r="117" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="37"/>
@@ -13773,7 +13147,7 @@
       <c r="AH117" s="1"/>
       <c r="AI117" s="1"/>
     </row>
-    <row r="118" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="37"/>
@@ -13810,7 +13184,7 @@
       <c r="AH118" s="1"/>
       <c r="AI118" s="1"/>
     </row>
-    <row r="119" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="37"/>
@@ -13847,7 +13221,7 @@
       <c r="AH119" s="1"/>
       <c r="AI119" s="1"/>
     </row>
-    <row r="120" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="37"/>
@@ -13884,7 +13258,7 @@
       <c r="AH120" s="1"/>
       <c r="AI120" s="1"/>
     </row>
-    <row r="121" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" ht="18" x14ac:dyDescent="0.35">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="37"/>
@@ -13921,15 +13295,15 @@
       <c r="AH121" s="1"/>
       <c r="AI121" s="1"/>
     </row>
-    <row r="122" spans="1:35" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:35" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="38"/>
-      <c r="D122" s="81"/>
+      <c r="D122" s="60"/>
       <c r="E122" s="39"/>
       <c r="F122" s="40"/>
       <c r="G122" s="39"/>
-      <c r="H122" s="79"/>
+      <c r="H122" s="58"/>
       <c r="I122" s="9"/>
       <c r="J122" s="54"/>
       <c r="K122" s="29"/>
@@ -13958,7 +13332,7 @@
       <c r="AH122" s="1"/>
       <c r="AI122" s="1"/>
     </row>
-    <row r="123" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -13995,7 +13369,7 @@
       <c r="AH123" s="1"/>
       <c r="AI123" s="1"/>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -14032,7 +13406,7 @@
       <c r="AH124" s="1"/>
       <c r="AI124" s="1"/>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -14069,7 +13443,7 @@
       <c r="AH125" s="1"/>
       <c r="AI125" s="1"/>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -14106,7 +13480,7 @@
       <c r="AH126" s="1"/>
       <c r="AI126" s="1"/>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -14143,7 +13517,7 @@
       <c r="AH127" s="1"/>
       <c r="AI127" s="1"/>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -14180,7 +13554,7 @@
       <c r="AH128" s="1"/>
       <c r="AI128" s="1"/>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -14217,7 +13591,7 @@
       <c r="AH129" s="1"/>
       <c r="AI129" s="1"/>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -14254,7 +13628,7 @@
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -14291,7 +13665,7 @@
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -14328,7 +13702,7 @@
       <c r="AH132" s="1"/>
       <c r="AI132" s="1"/>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -14365,7 +13739,7 @@
       <c r="AH133" s="1"/>
       <c r="AI133" s="1"/>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -14402,7 +13776,7 @@
       <c r="AH134" s="1"/>
       <c r="AI134" s="1"/>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -14439,7 +13813,7 @@
       <c r="AH135" s="1"/>
       <c r="AI135" s="1"/>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -14476,7 +13850,7 @@
       <c r="AH136" s="1"/>
       <c r="AI136" s="1"/>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -14513,7 +13887,7 @@
       <c r="AH137" s="1"/>
       <c r="AI137" s="1"/>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -14550,7 +13924,7 @@
       <c r="AH138" s="1"/>
       <c r="AI138" s="1"/>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -14590,6 +13964,13 @@
   </sheetData>
   <autoFilter ref="C9:H121" xr:uid="{48802423-A9B2-4292-96AC-09F2820DE26C}"/>
   <mergeCells count="15">
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="A1:B6"/>
+    <mergeCell ref="C2:H6"/>
+    <mergeCell ref="J2:K6"/>
+    <mergeCell ref="M11:N12"/>
+    <mergeCell ref="M17:N18"/>
     <mergeCell ref="J38:K39"/>
     <mergeCell ref="L38:O39"/>
     <mergeCell ref="M21:M22"/>
@@ -14598,13 +13979,6 @@
     <mergeCell ref="N24:N25"/>
     <mergeCell ref="M26:M28"/>
     <mergeCell ref="N26:N28"/>
-    <mergeCell ref="A1:B6"/>
-    <mergeCell ref="C2:H6"/>
-    <mergeCell ref="J2:K6"/>
-    <mergeCell ref="M11:N12"/>
-    <mergeCell ref="M17:N18"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N20"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H122">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
@@ -14614,19 +13988,19 @@
   <conditionalFormatting sqref="J10:J36">
     <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K10">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K10">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D10:D122" xr:uid="{5A9C7538-9203-418E-9754-4DC875330996}">
@@ -14653,7 +14027,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C685C2-5978-4EF9-ABEA-57D126402986}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
